--- a/inputs/Consolidado Sugeridos.xlsx
+++ b/inputs/Consolidado Sugeridos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoalicorp-my.sharepoint.com/personal/vcaceresc_alicorp_com_pe/Documents/Documentos/split_dashboard/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BB98F1CF-DDAE-4DE1-B847-F086F8CE927C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F737E6B-711F-490D-A277-399C7ED7D4FA}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BB98F1CF-DDAE-4DE1-B847-F086F8CE927C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5772126C-A866-458C-B8D4-675F35C7A4C4}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="10770" windowHeight="11010" activeTab="1" xr2:uid="{A471BADF-2A63-4EF0-84CA-68C120FA6EDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A471BADF-2A63-4EF0-84CA-68C120FA6EDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1174,7 +1174,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142FFBCE-9551-45B4-B922-DDCA863E4DB9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1204,7 +1203,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>1000032977</v>
       </c>
@@ -1224,7 +1223,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1000029686</v>
       </c>
@@ -1244,7 +1243,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>1000031185</v>
       </c>
@@ -1261,7 +1260,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>1000007880</v>
       </c>
@@ -1278,7 +1277,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>1000009363</v>
       </c>
@@ -1295,7 +1294,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>1000036516</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>1000007672</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>1000009584</v>
       </c>
@@ -1346,7 +1345,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>1000009232</v>
       </c>
@@ -1363,7 +1362,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>1000008179</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>1000008167</v>
       </c>
@@ -1397,7 +1396,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>1000018310</v>
       </c>
@@ -1414,7 +1413,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>1000009915</v>
       </c>
@@ -1431,7 +1430,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>1000010077</v>
       </c>
@@ -1448,7 +1447,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>1000018352</v>
       </c>
@@ -1465,7 +1464,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>1000008558</v>
       </c>
@@ -1482,7 +1481,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>1000012343</v>
       </c>
@@ -1499,7 +1498,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>1000012371</v>
       </c>
@@ -1516,7 +1515,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>1000019463</v>
       </c>
@@ -1533,7 +1532,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>1000035585</v>
       </c>
@@ -1550,7 +1549,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>1000009740</v>
       </c>
@@ -1567,7 +1566,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>1000008156</v>
       </c>
@@ -1584,7 +1583,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>1000009166</v>
       </c>
@@ -1601,7 +1600,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>1000009263</v>
       </c>
@@ -1618,7 +1617,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>1000007806</v>
       </c>
@@ -1635,7 +1634,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>1000033069</v>
       </c>
@@ -1652,7 +1651,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>1000010013</v>
       </c>
@@ -1669,7 +1668,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>1000008148</v>
       </c>
@@ -1686,7 +1685,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>1000018617</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>1000049409</v>
       </c>
@@ -1720,7 +1719,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>1000049410</v>
       </c>
@@ -1737,7 +1736,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>1000007641</v>
       </c>
@@ -1754,7 +1753,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>1000007598</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>1000002120</v>
       </c>
@@ -1788,7 +1787,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>1000018381</v>
       </c>
@@ -1805,7 +1804,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>1000008167</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>1000009584</v>
       </c>
@@ -1839,7 +1838,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>1000009232</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>1000007530</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>1000008179</v>
       </c>
@@ -1890,7 +1889,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>1000018847</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>1000035471</v>
       </c>
@@ -1924,7 +1923,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>1000007926</v>
       </c>
@@ -1941,7 +1940,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>1000021614</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>1000018378</v>
       </c>
@@ -1975,7 +1974,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>1000008558</v>
       </c>
@@ -1992,7 +1991,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>1000012329</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>1000035585</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>1000009740</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>1000008156</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>1000019463</v>
       </c>
@@ -2094,7 +2093,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>1000009166</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>1000012124</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>1000033069</v>
       </c>
@@ -2145,7 +2144,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>1000029441</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>1000007625</v>
       </c>
@@ -2179,7 +2178,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>1000009584</v>
       </c>
@@ -2196,7 +2195,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>1000009232</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>1000008179</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>1000008838</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>1000011855</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>1000018847</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>1000035471</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>1000008167</v>
       </c>
@@ -2315,7 +2314,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>1000018310</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>1000029696</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>1000009915</v>
       </c>
@@ -2366,7 +2365,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>1000007536</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>1000018378</v>
       </c>
@@ -2400,7 +2399,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>1000009486</v>
       </c>
@@ -2417,7 +2416,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>1000008156</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>1000008160</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>1000008396</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>1000018430</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>1000018661</v>
       </c>
@@ -2502,7 +2501,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>1000000359</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>1000029686</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>1000019336</v>
       </c>
@@ -2556,7 +2555,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>1000019353</v>
       </c>
@@ -2576,7 +2575,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>1000004025</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>1000007880</v>
       </c>
@@ -2610,7 +2609,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>1000023530</v>
       </c>
@@ -2627,7 +2626,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>1000018999</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>1000009039</v>
       </c>
@@ -2664,7 +2663,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>1000008402</v>
       </c>
@@ -2681,7 +2680,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>1000004006</v>
       </c>
@@ -2698,7 +2697,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>1000008179</v>
       </c>
@@ -2715,7 +2714,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>1000035471</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>1000007598</v>
       </c>
@@ -2749,7 +2748,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>1000032977</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>1000018661</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>1000000359</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>1000029686</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>1000018378</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>1000012371</v>
       </c>
@@ -2851,7 +2850,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>1000018534</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>1000008156</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>1000008899</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>1000008160</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>1000009166</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>1000007598</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>1000008167</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>1000018310</v>
       </c>
@@ -3004,7 +3003,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>1000029696</v>
       </c>
@@ -3021,7 +3020,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>1000009915</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>1000007536</v>
       </c>
@@ -3056,13 +3055,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F109" xr:uid="{142FFBCE-9551-45B4-B922-DDCA863E4DB9}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1000036437"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F109" xr:uid="{142FFBCE-9551-45B4-B922-DDCA863E4DB9}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
